--- a/results/q4_output/扩容优先级.xlsx
+++ b/results/q4_output/扩容优先级.xlsx
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.6952</v>
+        <v>0.736</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1234</v>
+        <v>0.032</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.4095</v>
+        <v>0.3616</v>
       </c>
     </row>
     <row r="3">
@@ -520,10 +520,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.7373</v>
+        <v>0.7361</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1481</v>
+        <v>0.0267</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.3958</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="4">
@@ -544,18 +544,18 @@
         <v>2026</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.7493</v>
+        <v>0.7361</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1272</v>
+        <v>0.0222</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.3835</v>
+        <v>0.3586</v>
       </c>
     </row>
     <row r="5">
@@ -573,21 +573,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7743</v>
+        <v>0.7829</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1552</v>
+        <v>0.0344</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.3794</v>
+        <v>0.3389</v>
       </c>
     </row>
     <row r="6">
@@ -605,21 +605,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7829</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1128</v>
+        <v>0.0287</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.374</v>
+        <v>0.3372</v>
       </c>
     </row>
     <row r="7">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7837</v>
+        <v>0.7829</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1526</v>
+        <v>0.0239</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.3739</v>
+        <v>0.3357</v>
       </c>
     </row>
     <row r="8">
@@ -669,21 +669,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8051</v>
+        <v>0.7901</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1862</v>
+        <v>0.0354</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.3733</v>
+        <v>0.3356</v>
       </c>
     </row>
     <row r="9">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7577</v>
+        <v>0.7901</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1056</v>
+        <v>0.0295</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.3728</v>
+        <v>0.3338</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1354</v>
+        <v>0.0307</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.3642</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="11">
@@ -765,21 +765,21 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.7913</v>
+        <v>0.8044</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1267</v>
+        <v>0.0498</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.3624</v>
+        <v>0.3327</v>
       </c>
     </row>
     <row r="12">
@@ -800,18 +800,18 @@
         <v>2026</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8197</v>
+        <v>0.7901</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1565</v>
+        <v>0.0246</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -819,39 +819,39 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.3571</v>
+        <v>0.3323</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2027</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.142</v>
+        <v>0.0256</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.3563</v>
+        <v>0.3317</v>
       </c>
     </row>
     <row r="14">
@@ -861,21 +861,21 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.844</v>
+        <v>0.7919</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1878</v>
+        <v>0.0213</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -883,39 +883,39 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.3543</v>
+        <v>0.3305</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.6952</v>
+        <v>0.8045</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1234</v>
+        <v>0.0415</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.3507</v>
+        <v>0.3302</v>
       </c>
     </row>
     <row r="16">
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8565</v>
+        <v>0.8045</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1572</v>
+        <v>0.0346</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.3389</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="17">
@@ -957,21 +957,21 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9126</v>
+        <v>0.8438</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2502</v>
+        <v>0.0416</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.3388</v>
+        <v>0.3106</v>
       </c>
     </row>
     <row r="18">
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.8773</v>
+        <v>0.8439</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1778</v>
+        <v>0.0347</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.3347</v>
+        <v>0.3085</v>
       </c>
     </row>
     <row r="19">
@@ -1024,18 +1024,18 @@
         <v>2026</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.8996</v>
+        <v>0.8439</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2085</v>
+        <v>0.0289</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.3328</v>
+        <v>0.3067</v>
       </c>
     </row>
     <row r="20">
@@ -1053,21 +1053,21 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.7492</v>
+        <v>0.736</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1462</v>
+        <v>0.0294</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.3305</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="21">
@@ -1088,18 +1088,18 @@
         <v>2027</v>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.7743</v>
+        <v>0.7361</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1785</v>
+        <v>0.0255</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.3277</v>
+        <v>0.3009</v>
       </c>
     </row>
     <row r="22">
@@ -1120,18 +1120,18 @@
         <v>2026</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.7493</v>
+        <v>0.7361</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1272</v>
+        <v>0.0222</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.3248</v>
+        <v>0.2999</v>
       </c>
     </row>
     <row r="23">
@@ -1152,18 +1152,18 @@
         <v>2028</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9776</v>
+        <v>0.8883</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3003</v>
+        <v>0.0341</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1171,199 +1171,199 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.3213</v>
+        <v>0.2861</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.7743</v>
+        <v>0.8883</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1552</v>
+        <v>0.0284</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.3207</v>
+        <v>0.2844</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.8883</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1297</v>
+        <v>0.0237</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.3204</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8711</v>
+        <v>0.7829</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1199</v>
+        <v>0.0316</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.3204</v>
+        <v>0.2793</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9366</v>
+        <v>0.7829</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2253</v>
+        <v>0.0275</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.3193</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.7577</v>
+        <v>0.913</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1215</v>
+        <v>0.0449</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.3189</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.8887</v>
+        <v>0.7829</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1439</v>
+        <v>0.0239</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.3188</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="30">
@@ -1373,21 +1373,21 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7901</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1128</v>
+        <v>0.0325</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.3153</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="31">
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9195</v>
+        <v>0.913</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1831</v>
+        <v>0.0374</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.3152</v>
+        <v>0.2747</v>
       </c>
     </row>
     <row r="32">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C32" t="n">
         <v>10</v>
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.7577</v>
+        <v>0.7901</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1056</v>
+        <v>0.0283</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1459,113 +1459,113 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.3141</v>
+        <v>0.2747</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2028</v>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9565</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2235</v>
+        <v>0.0282</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.3088</v>
+        <v>0.2738</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.7901</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1554</v>
+        <v>0.0246</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.3067</v>
+        <v>0.2736</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.8197</v>
+        <v>0.9131</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1799</v>
+        <v>0.0312</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.3054</v>
+        <v>0.2728</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C36" t="n">
         <v>4</v>
@@ -1576,18 +1576,18 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9308</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1625</v>
+        <v>0.0245</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.3033</v>
+        <v>0.2727</v>
       </c>
     </row>
     <row r="37">
@@ -1597,21 +1597,21 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.8197</v>
+        <v>0.8045</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1565</v>
+        <v>0.0457</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1619,135 +1619,135 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.2983</v>
+        <v>0.2727</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.7919</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1358</v>
+        <v>0.0213</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.2982</v>
+        <v>0.2717</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>2027</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9224</v>
+        <v>0.8045</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1295</v>
+        <v>0.0398</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.2977</v>
+        <v>0.2709</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>2026</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9106</v>
+        <v>0.8045</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1079</v>
+        <v>0.0346</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.2971</v>
+        <v>0.2694</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.6952</v>
+        <v>0.9226</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1234</v>
+        <v>0.0316</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.2945</v>
+        <v>0.2682</v>
       </c>
     </row>
     <row r="42">
@@ -1757,21 +1757,21 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9557</v>
+        <v>0.9226</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1727</v>
+        <v>0.0263</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.2939</v>
+        <v>0.2666</v>
       </c>
     </row>
     <row r="43">
@@ -1789,21 +1789,21 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9555</v>
+        <v>0.9226</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1521</v>
+        <v>0.0219</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1811,167 +1811,167 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.2879</v>
+        <v>0.2653</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.8995</v>
+        <v>0.9564</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2398</v>
+        <v>0.0315</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.2834</v>
+        <v>0.2512</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9549</v>
+        <v>0.8438</v>
       </c>
       <c r="F45" t="n">
-        <v>0.132</v>
+        <v>0.0382</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.2821</v>
+        <v>0.2508</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.8595</v>
+        <v>0.9565</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1633</v>
+        <v>0.0262</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.2805</v>
+        <v>0.2496</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9497</v>
+        <v>0.8439</v>
       </c>
       <c r="F47" t="n">
-        <v>0.11</v>
+        <v>0.0332</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.2781</v>
+        <v>0.2493</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.8966</v>
+        <v>0.9565</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2052</v>
+        <v>0.0219</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.2745</v>
+        <v>0.2483</v>
       </c>
     </row>
     <row r="49">
@@ -1984,18 +1984,18 @@
         <v>2026</v>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.8996</v>
+        <v>0.8439</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2085</v>
+        <v>0.0289</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.274</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="50">
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.7492</v>
+        <v>0.7361</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1399</v>
+        <v>0.0269</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.2723</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="51">
@@ -2048,18 +2048,18 @@
         <v>2027</v>
       </c>
       <c r="C51" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.7743</v>
+        <v>0.7361</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1707</v>
+        <v>0.0244</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2067,71 +2067,71 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.2691</v>
+        <v>0.2443</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8858</v>
+        <v>0.7361</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1682</v>
+        <v>0.0222</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.2688</v>
+        <v>0.2436</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.7493</v>
+        <v>0.8883</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1272</v>
+        <v>0.0314</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.2685</v>
+        <v>0.2265</v>
       </c>
     </row>
     <row r="54">
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.951</v>
+        <v>0.8883</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2758</v>
+        <v>0.0273</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.2685</v>
+        <v>0.2253</v>
       </c>
     </row>
     <row r="55">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C55" t="n">
         <v>8</v>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.871</v>
+        <v>0.8883</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1379</v>
+        <v>0.0237</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2195,39 +2195,39 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.2671</v>
+        <v>0.2242</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>2028</v>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9162</v>
+        <v>0.7829</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2069</v>
+        <v>0.0289</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.2652</v>
+        <v>0.2222</v>
       </c>
     </row>
     <row r="57">
@@ -2237,21 +2237,21 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C57" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.7743</v>
+        <v>0.7829</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1552</v>
+        <v>0.0263</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.2644</v>
+        <v>0.2214</v>
       </c>
     </row>
     <row r="58">
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7829</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1241</v>
+        <v>0.0239</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2291,39 +2291,39 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.2624</v>
+        <v>0.2207</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8711</v>
+        <v>0.7901</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1199</v>
+        <v>0.0297</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.2617</v>
+        <v>0.2189</v>
       </c>
     </row>
     <row r="60">
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.7577</v>
+        <v>0.7901</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1162</v>
+        <v>0.027</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2355,71 +2355,71 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.261</v>
+        <v>0.2181</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.7901</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1492</v>
+        <v>0.0246</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.2602</v>
+        <v>0.2173</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.913</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1128</v>
+        <v>0.0412</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.259</v>
+        <v>0.2171</v>
       </c>
     </row>
     <row r="63">
@@ -2429,21 +2429,21 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C63" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.7577</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1056</v>
+        <v>0.0258</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2451,39 +2451,39 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.2578</v>
+        <v>0.2168</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C64" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8911</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1397</v>
+        <v>0.0234</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.2576</v>
+        <v>0.2161</v>
       </c>
     </row>
     <row r="65">
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9117</v>
+        <v>0.913</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1454</v>
+        <v>0.0358</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.249</v>
+        <v>0.2155</v>
       </c>
     </row>
     <row r="66">
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8197</v>
+        <v>0.7919</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1721</v>
+        <v>0.0213</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2547,39 +2547,39 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.2468</v>
+        <v>0.2155</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9106</v>
+        <v>0.8045</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1241</v>
+        <v>0.0418</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.2432</v>
+        <v>0.2153</v>
       </c>
     </row>
     <row r="68">
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8197</v>
+        <v>0.8045</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1565</v>
+        <v>0.038</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2611,71 +2611,71 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.2421</v>
+        <v>0.2142</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.8174</v>
+        <v>0.9131</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1494</v>
+        <v>0.0312</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.2411</v>
+        <v>0.2141</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>2026</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9106</v>
+        <v>0.8045</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1079</v>
+        <v>0.0346</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.2383</v>
+        <v>0.2131</v>
       </c>
     </row>
     <row r="71">
@@ -2688,18 +2688,18 @@
         <v>2028</v>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9412</v>
+        <v>0.9226</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1586</v>
+        <v>0.029</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2707,135 +2707,135 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.2382</v>
+        <v>0.2087</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C72" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.8637</v>
+        <v>0.9226</v>
       </c>
       <c r="F72" t="n">
-        <v>0.1878</v>
+        <v>0.0252</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.2295</v>
+        <v>0.2075</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.8491</v>
+        <v>0.9226</v>
       </c>
       <c r="F73" t="n">
-        <v>0.1539</v>
+        <v>0.0219</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.2266</v>
+        <v>0.2065</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>2028</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.8439</v>
       </c>
       <c r="F74" t="n">
-        <v>0.1427</v>
+        <v>0.035</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.2255</v>
+        <v>0.1936</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>2027</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9497</v>
+        <v>0.8439</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1265</v>
+        <v>0.0318</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.2244</v>
+        <v>0.1926</v>
       </c>
     </row>
     <row r="76">
@@ -2845,21 +2845,21 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C76" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.8995</v>
+        <v>0.8439</v>
       </c>
       <c r="F76" t="n">
-        <v>0.2294</v>
+        <v>0.0289</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.224</v>
+        <v>0.1917</v>
       </c>
     </row>
     <row r="77">
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C77" t="n">
         <v>2</v>
@@ -2888,10 +2888,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.9497</v>
+        <v>0.9564</v>
       </c>
       <c r="F77" t="n">
-        <v>0.11</v>
+        <v>0.0289</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2899,71 +2899,71 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.2194</v>
+        <v>0.1917</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.856</v>
+        <v>0.9565</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1365</v>
+        <v>0.0251</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.2179</v>
+        <v>0.1906</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>2026</v>
       </c>
       <c r="C79" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8996</v>
+        <v>0.9565</v>
       </c>
       <c r="F79" t="n">
-        <v>0.2085</v>
+        <v>0.0219</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.2178</v>
+        <v>0.1896</v>
       </c>
     </row>
     <row r="80">
@@ -2976,18 +2976,18 @@
         <v>2028</v>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8903</v>
+        <v>0.8883</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1893</v>
+        <v>0.0287</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.2166</v>
+        <v>0.1695</v>
       </c>
     </row>
     <row r="81">
@@ -3005,21 +3005,21 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C81" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8551</v>
+        <v>0.8883</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1278</v>
+        <v>0.0261</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.2158</v>
+        <v>0.1687</v>
       </c>
     </row>
     <row r="82">
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.9374</v>
+        <v>0.8883</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2523</v>
+        <v>0.0237</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.212</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="83">
@@ -3069,21 +3069,21 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.8711</v>
+        <v>0.913</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1319</v>
+        <v>0.0377</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.209</v>
+        <v>0.1598</v>
       </c>
     </row>
     <row r="84">
@@ -3101,21 +3101,21 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.8711</v>
+        <v>0.913</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1199</v>
+        <v>0.0343</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.2054</v>
+        <v>0.1588</v>
       </c>
     </row>
     <row r="85">
@@ -3133,21 +3133,21 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9224</v>
+        <v>0.9131</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1451</v>
+        <v>0.0312</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.1873</v>
+        <v>0.1578</v>
       </c>
     </row>
     <row r="86">
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9106</v>
+        <v>0.9226</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1187</v>
+        <v>0.0265</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.1853</v>
+        <v>0.1517</v>
       </c>
     </row>
     <row r="87">
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9106</v>
+        <v>0.9226</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1079</v>
+        <v>0.0241</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.1821</v>
+        <v>0.1509</v>
       </c>
     </row>
     <row r="88">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9448</v>
+        <v>0.9226</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1306</v>
+        <v>0.0219</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0.1718</v>
+        <v>0.1503</v>
       </c>
     </row>
     <row r="89">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C89" t="n">
         <v>2</v>
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9497</v>
+        <v>0.9565</v>
       </c>
       <c r="F89" t="n">
-        <v>0.121</v>
+        <v>0.0264</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.1664</v>
+        <v>0.1347</v>
       </c>
     </row>
     <row r="90">
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C90" t="n">
         <v>2</v>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9617</v>
+        <v>0.9565</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1331</v>
+        <v>0.024</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.1641</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="91">
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9497</v>
+        <v>0.9565</v>
       </c>
       <c r="F91" t="n">
-        <v>0.11</v>
+        <v>0.0219</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0.1631</v>
+        <v>0.1333</v>
       </c>
     </row>
   </sheetData>

--- a/results/q4_output/扩容优先级.xlsx
+++ b/results/q4_output/扩容优先级.xlsx
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.736</v>
+        <v>0.7006</v>
       </c>
       <c r="F2" t="n">
-        <v>0.032</v>
+        <v>0.1227</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.3616</v>
+        <v>0.4065</v>
       </c>
     </row>
     <row r="3">
@@ -512,18 +512,18 @@
         <v>2027</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.7361</v>
+        <v>0.7536</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0267</v>
+        <v>0.2092</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>0.406</v>
       </c>
     </row>
     <row r="4">
@@ -552,10 +552,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.7361</v>
+        <v>0.7007</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0222</v>
+        <v>0.1022</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.3586</v>
+        <v>0.4003</v>
       </c>
     </row>
     <row r="5">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7829</v>
+        <v>0.7536</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0344</v>
+        <v>0.1744</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.3389</v>
+        <v>0.3955</v>
       </c>
     </row>
     <row r="6">
@@ -608,18 +608,18 @@
         <v>2027</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7829</v>
+        <v>0.7637</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0287</v>
+        <v>0.1663</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.3372</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="7">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7829</v>
+        <v>0.8189</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0239</v>
+        <v>0.2511</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.3357</v>
+        <v>0.3859</v>
       </c>
     </row>
     <row r="8">
@@ -669,21 +669,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7901</v>
+        <v>0.7638</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0354</v>
+        <v>0.1386</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.3356</v>
+        <v>0.3797</v>
       </c>
     </row>
     <row r="9">
@@ -701,21 +701,21 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7901</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0295</v>
+        <v>0.1996</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.3338</v>
+        <v>0.3678</v>
       </c>
     </row>
     <row r="10">
@@ -733,21 +733,21 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.8228</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0307</v>
+        <v>0.1953</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.3333</v>
+        <v>0.3672</v>
       </c>
     </row>
     <row r="11">
@@ -765,21 +765,21 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8044</v>
+        <v>0.8228</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0498</v>
+        <v>0.1628</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -787,71 +787,71 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.3327</v>
+        <v>0.3574</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.7901</v>
+        <v>0.7006</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0246</v>
+        <v>0.1176</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.3323</v>
+        <v>0.3462</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2027</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7536</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0256</v>
+        <v>0.2005</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.3317</v>
+        <v>0.3446</v>
       </c>
     </row>
     <row r="14">
@@ -861,21 +861,21 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.7919</v>
+        <v>0.7784</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0213</v>
+        <v>0.0389</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -883,39 +883,39 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.3305</v>
+        <v>0.3425</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.8045</v>
+        <v>0.7007</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0415</v>
+        <v>0.1022</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.3302</v>
+        <v>0.3416</v>
       </c>
     </row>
     <row r="16">
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8045</v>
+        <v>0.7621</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0346</v>
+        <v>0.006</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.3281</v>
+        <v>0.3407</v>
       </c>
     </row>
     <row r="17">
@@ -957,21 +957,21 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8438</v>
+        <v>0.7785</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0416</v>
+        <v>0.0324</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.3106</v>
+        <v>0.3405</v>
       </c>
     </row>
     <row r="18">
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.8439</v>
+        <v>0.7621</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0347</v>
+        <v>0.005</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1011,45 +1011,45 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.3085</v>
+        <v>0.3404</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2026</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.8439</v>
+        <v>0.7536</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0289</v>
+        <v>0.1744</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.3067</v>
+        <v>0.3368</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1064,50 +1064,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.736</v>
+        <v>0.8633</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0294</v>
+        <v>0.1472</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.302</v>
+        <v>0.3325</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.7361</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0255</v>
+        <v>0.2344</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.3009</v>
+        <v>0.3324</v>
       </c>
     </row>
     <row r="22">
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.7361</v>
+        <v>0.7637</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0222</v>
+        <v>0.1594</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1139,39 +1139,39 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.2999</v>
+        <v>0.3272</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.8883</v>
+        <v>0.7638</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0341</v>
+        <v>0.1386</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.2861</v>
+        <v>0.3209</v>
       </c>
     </row>
     <row r="24">
@@ -1184,18 +1184,18 @@
         <v>2027</v>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.8883</v>
+        <v>0.9121</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0284</v>
+        <v>0.1803</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.2844</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="25">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C25" t="n">
         <v>8</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8883</v>
+        <v>0.8733</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0237</v>
+        <v>0.091</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1235,135 +1235,135 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.283</v>
+        <v>0.3107</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.7829</v>
+        <v>0.9121</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0316</v>
+        <v>0.1503</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.2793</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.7829</v>
+        <v>0.9569</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0275</v>
+        <v>0.2164</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.278</v>
+        <v>0.3065</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2028</v>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.913</v>
+        <v>0.8487</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0449</v>
+        <v>0.2306</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.277</v>
+        <v>0.3061</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2026</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.7829</v>
+        <v>0.8733</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0239</v>
+        <v>0.0759</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.277</v>
+        <v>0.3061</v>
       </c>
     </row>
     <row r="30">
@@ -1373,21 +1373,21 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.7901</v>
+        <v>0.8228</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0325</v>
+        <v>0.1872</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.276</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="31">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.913</v>
+        <v>0.9014</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0374</v>
+        <v>0.1215</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1427,71 +1427,71 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.2747</v>
+        <v>0.3057</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.7901</v>
+        <v>0.9014</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0283</v>
+        <v>0.1013</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.2747</v>
+        <v>0.2997</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.9505</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0282</v>
+        <v>0.1811</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.2738</v>
+        <v>0.2991</v>
       </c>
     </row>
     <row r="34">
@@ -1504,18 +1504,18 @@
         <v>2026</v>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.7901</v>
+        <v>0.8228</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0246</v>
+        <v>0.1628</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.2736</v>
+        <v>0.2987</v>
       </c>
     </row>
     <row r="35">
@@ -1533,21 +1533,21 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9131</v>
+        <v>0.9738</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0312</v>
+        <v>0.2173</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1555,103 +1555,103 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.2728</v>
+        <v>0.2983</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7006</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0245</v>
+        <v>0.1237</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.2727</v>
+        <v>0.2918</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>2028</v>
       </c>
       <c r="C37" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.8045</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0457</v>
+        <v>0.211</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.2727</v>
+        <v>0.2915</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>2026</v>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.7919</v>
+        <v>0.9505</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0213</v>
+        <v>0.1509</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.2717</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="39">
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.8045</v>
+        <v>0.8548</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0398</v>
+        <v>0.1833</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1683,39 +1683,39 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.2709</v>
+        <v>0.2888</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.8045</v>
+        <v>0.7006</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0346</v>
+        <v>0.1125</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.2694</v>
+        <v>0.2884</v>
       </c>
     </row>
     <row r="41">
@@ -1728,18 +1728,18 @@
         <v>2028</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9226</v>
+        <v>0.9537</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0316</v>
+        <v>0.1458</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1747,231 +1747,231 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.2682</v>
+        <v>0.2869</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>2027</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9226</v>
+        <v>0.7536</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0263</v>
+        <v>0.1918</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.2666</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9226</v>
+        <v>0.8325</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0219</v>
+        <v>0.1352</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.2653</v>
+        <v>0.2856</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9564</v>
+        <v>0.7007</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0315</v>
+        <v>0.1022</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.2512</v>
+        <v>0.2853</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2028</v>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.8438</v>
+        <v>0.8993</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0382</v>
+        <v>0.0467</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.2508</v>
+        <v>0.2844</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>2027</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9565</v>
+        <v>0.7785</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0262</v>
+        <v>0.0373</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.2496</v>
+        <v>0.2832</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.8439</v>
+        <v>0.9408</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0332</v>
+        <v>0.1093</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.2493</v>
+        <v>0.2824</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9565</v>
+        <v>0.7621</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0219</v>
+        <v>0.0057</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.2483</v>
+        <v>0.2819</v>
       </c>
     </row>
     <row r="49">
@@ -1984,18 +1984,18 @@
         <v>2026</v>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.8439</v>
+        <v>0.7785</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0289</v>
+        <v>0.0324</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2003,39 +2003,39 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.248</v>
+        <v>0.2818</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.7361</v>
+        <v>0.7621</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0269</v>
+        <v>0.005</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.245</v>
+        <v>0.2817</v>
       </c>
     </row>
     <row r="51">
@@ -2045,21 +2045,21 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.7361</v>
+        <v>0.7536</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0244</v>
+        <v>0.1744</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2067,135 +2067,135 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.2443</v>
+        <v>0.2805</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.7361</v>
+        <v>0.8984</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0222</v>
+        <v>0.2152</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.2436</v>
+        <v>0.2766</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>2028</v>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.8883</v>
+        <v>0.8925</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0314</v>
+        <v>0.0072</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.2265</v>
+        <v>0.2759</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8883</v>
+        <v>0.7637</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0273</v>
+        <v>0.1677</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.2253</v>
+        <v>0.2734</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8883</v>
+        <v>0.7638</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0237</v>
+        <v>0.1524</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.2242</v>
+        <v>0.2689</v>
       </c>
     </row>
     <row r="56">
@@ -2205,21 +2205,21 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.7829</v>
+        <v>0.7638</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0289</v>
+        <v>0.1386</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2227,39 +2227,39 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.2222</v>
+        <v>0.2647</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>2027</v>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.7829</v>
+        <v>0.9121</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0263</v>
+        <v>0.1728</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.2214</v>
+        <v>0.257</v>
       </c>
     </row>
     <row r="58">
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.7829</v>
+        <v>0.8228</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0239</v>
+        <v>0.1969</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2291,327 +2291,327 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.2207</v>
+        <v>0.2527</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.7901</v>
+        <v>0.8733</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0297</v>
+        <v>0.0873</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.2189</v>
+        <v>0.2508</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.7901</v>
+        <v>0.9121</v>
       </c>
       <c r="F60" t="n">
-        <v>0.027</v>
+        <v>0.1503</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.2181</v>
+        <v>0.2503</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>2026</v>
       </c>
       <c r="C61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.7901</v>
+        <v>0.8733</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0246</v>
+        <v>0.0759</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.2173</v>
+        <v>0.2474</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.913</v>
+        <v>0.8228</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0412</v>
+        <v>0.179</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.2171</v>
+        <v>0.2473</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>2028</v>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.9486</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0258</v>
+        <v>0.1987</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.2168</v>
+        <v>0.2466</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>2027</v>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.9014</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0234</v>
+        <v>0.1164</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.2161</v>
+        <v>0.2455</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.913</v>
+        <v>0.8228</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0358</v>
+        <v>0.1628</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.2155</v>
+        <v>0.2424</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>2026</v>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.7919</v>
+        <v>0.9014</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0213</v>
+        <v>0.1013</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.2155</v>
+        <v>0.2409</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C67" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8045</v>
+        <v>0.9505</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0418</v>
+        <v>0.1736</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.2153</v>
+        <v>0.2381</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C68" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8045</v>
+        <v>0.9696</v>
       </c>
       <c r="F68" t="n">
-        <v>0.038</v>
+        <v>0.1996</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.2142</v>
+        <v>0.2363</v>
       </c>
     </row>
     <row r="69">
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9131</v>
+        <v>0.8764</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0312</v>
+        <v>0.0429</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2643,39 +2643,39 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.2141</v>
+        <v>0.2359</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>2026</v>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.8045</v>
+        <v>0.9505</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0346</v>
+        <v>0.1509</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.2131</v>
+        <v>0.2313</v>
       </c>
     </row>
     <row r="71">
@@ -2688,18 +2688,18 @@
         <v>2028</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9226</v>
+        <v>0.9439</v>
       </c>
       <c r="F71" t="n">
-        <v>0.029</v>
+        <v>0.1339</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.2087</v>
+        <v>0.2295</v>
       </c>
     </row>
     <row r="72">
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9226</v>
+        <v>0.8678</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0252</v>
+        <v>0.0066</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2739,71 +2739,71 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.2075</v>
+        <v>0.2293</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9226</v>
+        <v>0.7784</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0219</v>
+        <v>0.0393</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.2065</v>
+        <v>0.2276</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>2028</v>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.8439</v>
+        <v>0.9281</v>
       </c>
       <c r="F74" t="n">
-        <v>0.035</v>
+        <v>0.1003</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.1936</v>
+        <v>0.2273</v>
       </c>
     </row>
     <row r="75">
@@ -2816,18 +2816,18 @@
         <v>2027</v>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.8439</v>
+        <v>0.7785</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0318</v>
+        <v>0.0357</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.1926</v>
+        <v>0.2265</v>
       </c>
     </row>
     <row r="76">
@@ -2845,21 +2845,21 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.8439</v>
+        <v>0.7621</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0289</v>
+        <v>0.006</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2867,103 +2867,103 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.1917</v>
+        <v>0.2258</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.9564</v>
+        <v>0.7621</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0289</v>
+        <v>0.0055</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.1917</v>
+        <v>0.2256</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>姚店镇</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.9565</v>
+        <v>0.7785</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0251</v>
+        <v>0.0324</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.1906</v>
+        <v>0.2255</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>2026</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>李渠镇</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.9565</v>
+        <v>0.7621</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0219</v>
+        <v>0.005</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.1896</v>
+        <v>0.2254</v>
       </c>
     </row>
     <row r="80">
@@ -2976,18 +2976,18 @@
         <v>2028</v>
       </c>
       <c r="C80" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8883</v>
+        <v>0.9121</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0287</v>
+        <v>0.1818</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.1695</v>
+        <v>0.2035</v>
       </c>
     </row>
     <row r="81">
@@ -3008,18 +3008,18 @@
         <v>2027</v>
       </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8883</v>
+        <v>0.9121</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0261</v>
+        <v>0.1653</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.1687</v>
+        <v>0.1985</v>
       </c>
     </row>
     <row r="82">
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C82" t="n">
         <v>8</v>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8883</v>
+        <v>0.8733</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0237</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.168</v>
+        <v>0.1959</v>
       </c>
     </row>
     <row r="83">
@@ -3069,21 +3069,21 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C83" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.913</v>
+        <v>0.9121</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0377</v>
+        <v>0.1503</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.1598</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="84">
@@ -3104,18 +3104,18 @@
         <v>2027</v>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.913</v>
+        <v>0.8733</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0343</v>
+        <v>0.0835</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.1588</v>
+        <v>0.1934</v>
       </c>
     </row>
     <row r="85">
@@ -3136,18 +3136,18 @@
         <v>2026</v>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9131</v>
+        <v>0.8733</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0312</v>
+        <v>0.0759</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.1578</v>
+        <v>0.1911</v>
       </c>
     </row>
     <row r="86">
@@ -3168,18 +3168,18 @@
         <v>2028</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9226</v>
+        <v>0.9014</v>
       </c>
       <c r="F86" t="n">
-        <v>0.0265</v>
+        <v>0.1225</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.1517</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="87">
@@ -3200,18 +3200,18 @@
         <v>2027</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9226</v>
+        <v>0.9014</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0241</v>
+        <v>0.1114</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.1509</v>
+        <v>0.1877</v>
       </c>
     </row>
     <row r="88">
@@ -3232,18 +3232,18 @@
         <v>2026</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>柳林镇</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9226</v>
+        <v>0.9014</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0219</v>
+        <v>0.1013</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0.1503</v>
+        <v>0.1847</v>
       </c>
     </row>
     <row r="89">
@@ -3272,10 +3272,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9565</v>
+        <v>0.9505</v>
       </c>
       <c r="F89" t="n">
-        <v>0.0264</v>
+        <v>0.1826</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.1347</v>
+        <v>0.1845</v>
       </c>
     </row>
     <row r="90">
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9565</v>
+        <v>0.9505</v>
       </c>
       <c r="F90" t="n">
-        <v>0.024</v>
+        <v>0.166</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.134</v>
+        <v>0.1796</v>
       </c>
     </row>
     <row r="91">
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9565</v>
+        <v>0.9505</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0219</v>
+        <v>0.1509</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0.1333</v>
+        <v>0.175</v>
       </c>
     </row>
   </sheetData>

--- a/results/q4_output/扩容优先级.xlsx
+++ b/results/q4_output/扩容优先级.xlsx
@@ -477,21 +477,21 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.7006</v>
+        <v>0.784</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1227</v>
+        <v>0.4725</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.4065</v>
+        <v>0.4697</v>
       </c>
     </row>
     <row r="3">
@@ -509,21 +509,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.7536</v>
+        <v>0.6219</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2092</v>
+        <v>0.1021</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.406</v>
+        <v>0.4397</v>
       </c>
     </row>
     <row r="4">
@@ -541,21 +541,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.7007</v>
+        <v>0.6763</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1022</v>
+        <v>0.1427</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.4003</v>
+        <v>0.4247</v>
       </c>
     </row>
     <row r="5">
@@ -576,18 +576,18 @@
         <v>2026</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7536</v>
+        <v>0.6679</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1744</v>
+        <v>0.0804</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.3955</v>
+        <v>0.4102</v>
       </c>
     </row>
     <row r="6">
@@ -608,18 +608,18 @@
         <v>2027</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7637</v>
+        <v>0.7048</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1663</v>
+        <v>0.1207</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.388</v>
+        <v>0.4038</v>
       </c>
     </row>
     <row r="7">
@@ -637,21 +637,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8189</v>
+        <v>0.895</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2511</v>
+        <v>0.4043</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.3859</v>
+        <v>0.3938</v>
       </c>
     </row>
     <row r="8">
@@ -669,21 +669,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7638</v>
+        <v>0.7284</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1386</v>
+        <v>0.1142</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -691,39 +691,39 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.3797</v>
+        <v>0.3901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.6219</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1996</v>
+        <v>0.1021</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.3678</v>
+        <v>0.3809</v>
       </c>
     </row>
     <row r="10">
@@ -736,18 +736,18 @@
         <v>2027</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.8228</v>
+        <v>0.7389</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1953</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -755,71 +755,71 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.3672</v>
+        <v>0.3791</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8228</v>
+        <v>0.8269</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1628</v>
+        <v>0.4339</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.3574</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.7006</v>
+        <v>0.9065</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1176</v>
+        <v>0.3369</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.3462</v>
+        <v>0.3678</v>
       </c>
     </row>
     <row r="13">
@@ -832,18 +832,18 @@
         <v>2027</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.7536</v>
+        <v>0.6851</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2005</v>
+        <v>0.1157</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -851,39 +851,39 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.3446</v>
+        <v>0.3534</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.7784</v>
+        <v>0.6679</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0389</v>
+        <v>0.0804</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.3425</v>
+        <v>0.3514</v>
       </c>
     </row>
     <row r="15">
@@ -893,21 +893,21 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.7007</v>
+        <v>0.7053</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1022</v>
+        <v>0.1311</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.3416</v>
+        <v>0.3479</v>
       </c>
     </row>
     <row r="16">
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.7621</v>
+        <v>0.8224</v>
       </c>
       <c r="F16" t="n">
-        <v>0.006</v>
+        <v>0.118</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.3407</v>
+        <v>0.3442</v>
       </c>
     </row>
     <row r="17">
@@ -957,21 +957,21 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.7785</v>
+        <v>0.863</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0324</v>
+        <v>0.1699</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.3405</v>
+        <v>0.3395</v>
       </c>
     </row>
     <row r="18">
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.7621</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.005</v>
+        <v>0.221</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1011,39 +1011,39 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.3404</v>
+        <v>0.3349</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.7536</v>
+        <v>0.614</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1744</v>
+        <v>0.1107</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.3368</v>
+        <v>0.3312</v>
       </c>
     </row>
     <row r="20">
@@ -1056,18 +1056,18 @@
         <v>2028</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8633</v>
+        <v>0.8852</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1472</v>
+        <v>0.177</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.3325</v>
+        <v>0.3305</v>
       </c>
     </row>
     <row r="21">
@@ -1085,21 +1085,21 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.8683</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2344</v>
+        <v>0.1416</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.3324</v>
+        <v>0.3283</v>
       </c>
     </row>
     <row r="22">
@@ -1120,18 +1120,18 @@
         <v>2027</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.7637</v>
+        <v>0.7214</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1594</v>
+        <v>0.0912</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.3272</v>
+        <v>0.3279</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1156,54 +1156,54 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.7638</v>
+        <v>0.8616</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1386</v>
+        <v>0.1229</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.3209</v>
+        <v>0.3261</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9121</v>
+        <v>0.6219</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1803</v>
+        <v>0.1021</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.318</v>
+        <v>0.3247</v>
       </c>
     </row>
     <row r="25">
@@ -1213,21 +1213,21 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8733</v>
+        <v>0.883</v>
       </c>
       <c r="F25" t="n">
-        <v>0.091</v>
+        <v>0.1475</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1235,39 +1235,39 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.3107</v>
+        <v>0.3228</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9121</v>
+        <v>0.9133</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1503</v>
+        <v>0.3874</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.309</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="27">
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9569</v>
+        <v>0.8956</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2164</v>
+        <v>0.1475</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.3065</v>
+        <v>0.3164</v>
       </c>
     </row>
     <row r="28">
@@ -1312,18 +1312,18 @@
         <v>2028</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.8487</v>
+        <v>0.7527</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2306</v>
+        <v>0.1049</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.3061</v>
+        <v>0.3163</v>
       </c>
     </row>
     <row r="29">
@@ -1344,18 +1344,18 @@
         <v>2026</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.8733</v>
+        <v>0.9019</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0759</v>
+        <v>0.1534</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1363,13 +1363,13 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.3061</v>
+        <v>0.3151</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1380,54 +1380,54 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.8228</v>
+        <v>0.9256</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1872</v>
+        <v>0.1841</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.306</v>
+        <v>0.3124</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9014</v>
+        <v>0.9065</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1215</v>
+        <v>0.3369</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.3057</v>
+        <v>0.3091</v>
       </c>
     </row>
     <row r="32">
@@ -1437,21 +1437,21 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9014</v>
+        <v>0.9171</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1013</v>
+        <v>0.1469</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1459,71 +1459,71 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.2997</v>
+        <v>0.3055</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2027</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9505</v>
+        <v>0.6585</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1811</v>
+        <v>0.0872</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.2991</v>
+        <v>0.3019</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>2026</v>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.8228</v>
+        <v>0.6679</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1628</v>
+        <v>0.0804</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.2987</v>
+        <v>0.2952</v>
       </c>
     </row>
     <row r="35">
@@ -1536,18 +1536,18 @@
         <v>2028</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9738</v>
+        <v>0.9669</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2173</v>
+        <v>0.1833</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.2983</v>
+        <v>0.2916</v>
       </c>
     </row>
     <row r="36">
@@ -1568,18 +1568,18 @@
         <v>2028</v>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.7006</v>
+        <v>0.7</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1237</v>
+        <v>0.1199</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.2918</v>
+        <v>0.291</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1608,242 +1608,242 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.9515</v>
       </c>
       <c r="F37" t="n">
-        <v>0.211</v>
+        <v>0.1391</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.2915</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>2026</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9505</v>
+        <v>0.8224</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1509</v>
+        <v>0.118</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.29</v>
+        <v>0.2854</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.8548</v>
+        <v>0.9326</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1833</v>
+        <v>0.102</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.2888</v>
+        <v>0.2843</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>2027</v>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.7006</v>
+        <v>0.9475</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1125</v>
+        <v>0.1224</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.2884</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2028</v>
       </c>
       <c r="C41" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9537</v>
+        <v>0.892</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1458</v>
+        <v>0.4076</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.2869</v>
+        <v>0.2813</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>2027</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.7536</v>
+        <v>0.9694</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1918</v>
+        <v>0.1528</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.2857</v>
+        <v>0.2811</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.8325</v>
+        <v>0.9411</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1352</v>
+        <v>0.1024</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.2856</v>
+        <v>0.2802</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>新城街道</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.7007</v>
+        <v>0.9539</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1022</v>
+        <v>0.1229</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.2853</v>
+        <v>0.2799</v>
       </c>
     </row>
     <row r="45">
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.8993</v>
+        <v>0.9609</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0467</v>
+        <v>0.1273</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1875,39 +1875,39 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.2844</v>
+        <v>0.2778</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>高增长(20%)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C46" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.7785</v>
+        <v>0.9458</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0373</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.2832</v>
+        <v>0.2761</v>
       </c>
     </row>
     <row r="47">
@@ -1917,21 +1917,21 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9408</v>
+        <v>0.9577</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1093</v>
+        <v>0.1159</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.2824</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="48">
@@ -1952,18 +1952,18 @@
         <v>2027</v>
       </c>
       <c r="C48" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.7621</v>
+        <v>0.8597</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0057</v>
+        <v>0.1357</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.2819</v>
+        <v>0.2721</v>
       </c>
     </row>
     <row r="49">
@@ -1981,21 +1981,21 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.7785</v>
+        <v>0.8752</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0324</v>
+        <v>0.1561</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.2818</v>
+        <v>0.2705</v>
       </c>
     </row>
     <row r="50">
@@ -2016,18 +2016,18 @@
         <v>2026</v>
       </c>
       <c r="C50" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.7621</v>
+        <v>0.8616</v>
       </c>
       <c r="F50" t="n">
-        <v>0.005</v>
+        <v>0.1229</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.2817</v>
+        <v>0.2673</v>
       </c>
     </row>
     <row r="51">
@@ -2045,21 +2045,21 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.7536</v>
+        <v>0.7328</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1744</v>
+        <v>0.0946</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.2805</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="52">
@@ -2080,7 +2080,7 @@
         <v>2028</v>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8984</v>
+        <v>0.8952</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2152</v>
+        <v>0.1626</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2099,84 +2099,84 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.2766</v>
+        <v>0.2624</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.8925</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0072</v>
+        <v>0.3706</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.2759</v>
+        <v>0.2623</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C54" t="n">
         <v>4</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.7637</v>
+        <v>0.889</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1677</v>
+        <v>0.1414</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.2734</v>
+        <v>0.2592</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2184,31 +2184,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.7638</v>
+        <v>0.9291</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1524</v>
+        <v>0.2029</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.2689</v>
+        <v>0.2576</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>2026</v>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2216,18 +2216,18 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.7638</v>
+        <v>0.9019</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1386</v>
+        <v>0.1534</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.2647</v>
+        <v>0.2563</v>
       </c>
     </row>
     <row r="57">
@@ -2240,18 +2240,18 @@
         <v>2027</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9121</v>
+        <v>0.9212</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1728</v>
+        <v>0.1765</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.257</v>
+        <v>0.2536</v>
       </c>
     </row>
     <row r="58">
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8228</v>
+        <v>0.9065</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1969</v>
+        <v>0.3369</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.2527</v>
+        <v>0.2528</v>
       </c>
     </row>
     <row r="59">
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8733</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0873</v>
+        <v>0.1354</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2323,39 +2323,39 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.2508</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.9121</v>
+        <v>0.8285</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1503</v>
+        <v>0.1298</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.2503</v>
+        <v>0.2297</v>
       </c>
     </row>
     <row r="61">
@@ -2365,21 +2365,21 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8733</v>
+        <v>0.9449</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0759</v>
+        <v>0.1349</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.2474</v>
+        <v>0.2293</v>
       </c>
     </row>
     <row r="62">
@@ -2397,21 +2397,21 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8228</v>
+        <v>0.8224</v>
       </c>
       <c r="F62" t="n">
-        <v>0.179</v>
+        <v>0.118</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.2473</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="63">
@@ -2432,18 +2432,18 @@
         <v>2028</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.9486</v>
+        <v>0.9695</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1987</v>
+        <v>0.1684</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.2466</v>
+        <v>0.227</v>
       </c>
     </row>
     <row r="64">
@@ -2461,21 +2461,21 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.9014</v>
+        <v>0.9326</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1164</v>
+        <v>0.102</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2483,39 +2483,39 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.2455</v>
+        <v>0.2256</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>低增长(10%)</t>
+          <t>基准增长(15%)</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8228</v>
+        <v>0.9445</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1628</v>
+        <v>0.1173</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.2424</v>
+        <v>0.2242</v>
       </c>
     </row>
     <row r="66">
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9014</v>
+        <v>0.9555</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1013</v>
+        <v>0.1278</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.2409</v>
+        <v>0.2218</v>
       </c>
     </row>
     <row r="67">
@@ -2557,21 +2557,21 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9505</v>
+        <v>0.9411</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1736</v>
+        <v>0.1024</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.2381</v>
+        <v>0.2214</v>
       </c>
     </row>
     <row r="68">
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9696</v>
+        <v>0.9678</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1996</v>
+        <v>0.1464</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.2363</v>
+        <v>0.2213</v>
       </c>
     </row>
     <row r="69">
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.8764</v>
+        <v>0.9514</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0429</v>
+        <v>0.1178</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.2359</v>
+        <v>0.2209</v>
       </c>
     </row>
     <row r="70">
@@ -2656,18 +2656,18 @@
         <v>2026</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9505</v>
+        <v>0.9609</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1509</v>
+        <v>0.1273</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.2313</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="71">
@@ -2685,21 +2685,21 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9439</v>
+        <v>0.9458</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1339</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.2295</v>
+        <v>0.2173</v>
       </c>
     </row>
     <row r="72">
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C72" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.8678</v>
+        <v>0.9553</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0066</v>
+        <v>0.1111</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.2293</v>
+        <v>0.2169</v>
       </c>
     </row>
     <row r="73">
@@ -2749,21 +2749,21 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C73" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.7784</v>
+        <v>0.8647</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0393</v>
+        <v>0.1352</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2771,20 +2771,20 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.2276</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>2028</v>
       </c>
       <c r="C74" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2792,18 +2792,18 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9281</v>
+        <v>0.873</v>
       </c>
       <c r="F74" t="n">
-        <v>0.1003</v>
+        <v>0.1428</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.2273</v>
+        <v>0.2113</v>
       </c>
     </row>
     <row r="75">
@@ -2813,21 +2813,21 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C75" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.7785</v>
+        <v>0.8616</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0357</v>
+        <v>0.1229</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.2265</v>
+        <v>0.2111</v>
       </c>
     </row>
     <row r="76">
@@ -2845,21 +2845,21 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.7621</v>
+        <v>0.9051</v>
       </c>
       <c r="F76" t="n">
-        <v>0.006</v>
+        <v>0.1688</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.2258</v>
+        <v>0.2031</v>
       </c>
     </row>
     <row r="77">
@@ -2877,21 +2877,21 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C77" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.7621</v>
+        <v>0.898</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0055</v>
+        <v>0.1487</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.2256</v>
+        <v>0.2006</v>
       </c>
     </row>
     <row r="78">
@@ -2912,18 +2912,18 @@
         <v>2026</v>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.7785</v>
+        <v>0.9019</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0324</v>
+        <v>0.1534</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.2255</v>
+        <v>0.2001</v>
       </c>
     </row>
     <row r="79">
@@ -2941,21 +2941,21 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.7621</v>
+        <v>0.9281</v>
       </c>
       <c r="F79" t="n">
-        <v>0.005</v>
+        <v>0.1857</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.2254</v>
+        <v>0.1966</v>
       </c>
     </row>
     <row r="80">
@@ -2973,21 +2973,21 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.9121</v>
+        <v>0.9332</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1818</v>
+        <v>0.1122</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.2035</v>
+        <v>0.172</v>
       </c>
     </row>
     <row r="81">
@@ -3005,21 +3005,21 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.9121</v>
+        <v>0.9326</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1653</v>
+        <v>0.102</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.1985</v>
+        <v>0.1693</v>
       </c>
     </row>
     <row r="82">
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C82" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8733</v>
+        <v>0.9417</v>
       </c>
       <c r="F82" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.1127</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.1959</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="83">
@@ -3069,21 +3069,21 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>宝塔山街道</t>
+          <t>南市街道</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9121</v>
+        <v>0.9482</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1503</v>
+        <v>0.1234</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.194</v>
+        <v>0.1679</v>
       </c>
     </row>
     <row r="84">
@@ -3104,18 +3104,18 @@
         <v>2027</v>
       </c>
       <c r="C84" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.8733</v>
+        <v>0.9617</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0835</v>
+        <v>0.14</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.1934</v>
+        <v>0.1662</v>
       </c>
     </row>
     <row r="85">
@@ -3133,21 +3133,21 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C85" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.8733</v>
+        <v>0.9702</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0759</v>
+        <v>0.154</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.1911</v>
+        <v>0.1661</v>
       </c>
     </row>
     <row r="86">
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9014</v>
+        <v>0.9411</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1225</v>
+        <v>0.1024</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.191</v>
+        <v>0.1652</v>
       </c>
     </row>
     <row r="87">
@@ -3197,21 +3197,21 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C87" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>宝塔山街道</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9014</v>
+        <v>0.9545</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1114</v>
+        <v>0.1239</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.1877</v>
+        <v>0.1649</v>
       </c>
     </row>
     <row r="88">
@@ -3229,21 +3229,21 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C88" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9014</v>
+        <v>0.9463</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1013</v>
+        <v>0.1063</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0.1847</v>
+        <v>0.1637</v>
       </c>
     </row>
     <row r="89">
@@ -3261,21 +3261,21 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>新城街道</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9505</v>
+        <v>0.9609</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1826</v>
+        <v>0.1273</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.1845</v>
+        <v>0.1628</v>
       </c>
     </row>
     <row r="90">
@@ -3293,21 +3293,21 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9505</v>
+        <v>0.9458</v>
       </c>
       <c r="F90" t="n">
-        <v>0.166</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.1796</v>
+        <v>0.1611</v>
       </c>
     </row>
     <row r="91">
@@ -3325,21 +3325,21 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>南市街道</t>
+          <t>凤凰山街道</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9505</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1509</v>
+        <v>0.1169</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0.175</v>
+        <v>0.161</v>
       </c>
     </row>
   </sheetData>
